--- a/equipment/bill-of-materials.xlsx
+++ b/equipment/bill-of-materials.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -158,6 +158,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,12 +574,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>In06_Потолочная, омни, MIMO, 800-2700 (G= 3dBi, H=360°)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Потолочная omni, MIMO; 800–2700 МГц; G=3 dBi; H=360°. Вертикальная диаграмма не предоставлена.</t>
         </is>
@@ -593,12 +599,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>PC211 Триплексер 1710-1880/1920-2170/2500-2690 МГц, одинарный, 4.3-10F, -160дБн, IP67</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Триплексер 1710–1880 / 1920–2170 / 2500–2690 МГц, одинарный; 4.3-10F; IP67. Insertion loss не дано.</t>
         </is>
@@ -618,12 +624,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>PC221_Гибридный комбайнер, 6дБ, 790-2700 МГц, 4.3-10F, -160дБн, IP65 (Комбайнер 4х4, 8 портов)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Гибрид 4×4, 8 портов; 790–2700 МГц; 6 дБ; 4.3-10F; IP65. Изоляция и допустимая мощность не даны.</t>
         </is>
@@ -643,12 +649,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>PC250_Делитель мощности, 2:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Делитель 2:1; 700–2700 МГц; 4.3-10F; IP65. Идеальное деление 3,01 дБ, excess loss не дано.</t>
         </is>
@@ -668,12 +674,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>PC252_Делитель мощности, 4:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Делитель 4:1; 700–2700 МГц; 4.3-10F; IP65. Идеальное деление 6,02 дБ, excess loss не дано.</t>
         </is>
@@ -693,12 +699,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Фидер коаксиальный 1/2 гибкий, оболочка - огнестойкая безгалогеновая</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>1/2, 50 Ом по PDF LCF12-50J; 10,09 / 10,99 / 12,3867 дБ/100м при 1800/2100/2600 (последние две интерполированы). Пожарная модификация не подтверждена.</t>
         </is>
@@ -718,12 +724,12 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Фидер коаксиальный 7/8 гибкий, оболочка - огнестойкая безгалогеновая</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>7/8, 50 Ом по PDF LCF78-50JA-A0; 5,21 / 5,67 / 6,39 дБ/100м при 1800/2100/2600; допуск ±5%. Пожарная модификация не подтверждена.</t>
         </is>
@@ -748,7 +754,7 @@
           <t xml:space="preserve">Разъем 4.3-10 для 1/2 </t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>4.3-10 для фидера 1/2. Loss, PIM и конкретная модификация не предоставлены.</t>
         </is>
@@ -773,7 +779,7 @@
           <t>Разъем 4.3-10 для 7/8</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>4.3-10 для фидера 7/8. Loss, PIM и конкретная модификация не предоставлены.</t>
         </is>
@@ -798,7 +804,7 @@
           <t>Джамп-кабель 4.3-10m / 4.3-10m 3м</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>4.3-10 male / 4.3-10 male, 3 м. Собственное затухание и тип кабеля не предоставлены.</t>
         </is>
@@ -1023,7 +1029,7 @@
       <c r="B2" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>50 Ом; модели и допустимые мощности не предоставлены, в основную спецификацию не добавлены</t>
         </is>
@@ -1038,7 +1044,7 @@
       <c r="B3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Четвёртые входы гибридов B1/B7; отдельного резерва GSM О2/О3 нет</t>
         </is>
@@ -1055,7 +1061,7 @@
           <t>34 male + 34 female</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Это требуемые исполнения в рамках общей позиции перечня; доступность не подтверждена</t>
         </is>
@@ -1072,7 +1078,7 @@
           <t>70 male + 30 female</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Female на антенных концах для male/male джамперов; переходники не выдуманы</t>
         </is>
@@ -1089,7 +1095,7 @@
           <t>Интерфейс не задан</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>4.3-10F на In06 принят как условие стыковки, не характеристика из перечня</t>
         </is>
@@ -1106,7 +1112,7 @@
           <t>Условно общий RF-порт БС</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>При раздельных выходах нужно дополнительное решение; его модели нет в исходных данных</t>
         </is>
@@ -1123,7 +1129,7 @@
           <t>Отдельных входов нет</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Три LTE-оператора предусмотрены, полное трёхоператорское использование GSM не подтверждено</t>
         </is>
@@ -1152,12 +1158,12 @@
           <t>PIM −160дБн</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Заявлено для пассивных компонентов в перечне</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Условия измерения, допустимая суммарная мощность и изоляция не предоставлены</t>
         </is>
@@ -1169,12 +1175,12 @@
           <t>Пожарное исполнение</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>XLSX: огнестойкое, безгалогеновое; PDF: PE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Расчёт затухания по PDF не подтверждает требуемую модификацию</t>
         </is>
@@ -1243,7 +1249,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>In06_Потолочная, омни, MIMO, 800-2700 (G= 3dBi, H=360°)</t>
         </is>
@@ -1263,7 +1269,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>In08_Панельная настенная, MIMO (G=7dBi, H=90°, V=60°)</t>
         </is>
@@ -1283,7 +1289,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>PC211 Триплексер 1710-1880/1920-2170/2500-2690 МГц, одинарный, 4.3-10F, -160дБн, IP67</t>
         </is>
@@ -1303,7 +1309,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>PC221_Гибридный комбайнер, 6дБ, 790-2700 МГц, 4.3-10F, -160дБн, IP65 (Комбайнер 4х4, 8 портов)</t>
         </is>
@@ -1323,7 +1329,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>PC250_Делитель мощности, 2:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1343,7 +1349,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>PC251_Делитель мощности, 3:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1363,7 +1369,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>PC252_Делитель мощности, 4:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1383,7 +1389,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>PC241_Направленный ответвитель, 7 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1403,7 +1409,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>PC243_Направленный ответвитель, 10 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1423,7 +1429,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>PC244_Направленный ответвитель, 13 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1443,7 +1449,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>PC245_Направленный ответвитель, 15 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
         </is>
@@ -1463,7 +1469,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Фидер коаксиальный 1/2 гибкий, оболочка - огнестойкая безгалогеновая</t>
         </is>
@@ -1483,7 +1489,7 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Фидер коаксиальный 7/8 гибкий, оболочка - огнестойкая безгалогеновая</t>
         </is>
@@ -1602,7 +1608,7 @@
           <t>Проект</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Расчётный вариант финала с явно указанными ограничениями; не комплект для закупки без проверки паспортов и условий монтажа</t>
         </is>
@@ -1614,7 +1620,7 @@
           <t>32 антенн</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Проектные точки выбраны из CAD-привязок и сравнения покрытия. Координаты, распределение и исходные IDs — в project-input.json. Помещение 89 не локализовано.</t>
         </is>
@@ -1626,7 +1632,7 @@
           <t>Дерево на одну MIMO-ветвь</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>PC221: 4 выхода → 4 PC211 → 4 зоны. В каждой зоне PC252: два выхода напрямую на две антенны; третий через PC250 на две; четвёртый через PC252 на четыре. Доли мощности 1/4, 1/8, 1/16; 2+2+4=8 антенн.</t>
         </is>
@@ -1638,7 +1644,7 @@
           <t>PC221</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>6: 3 диапазона × 2 MIMO-ветви. По три входа для операторов; четвёртый B3 для GSM МТС. Все четыре выхода используются. Неизвестные мощности других операторов не подставлены.</t>
         </is>
@@ -1650,7 +1656,7 @@
           <t>PC250</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>9: один делит DCS-пул на два гибрида B3; восемь питают парные подгруппы, по одному на зону/ветвь.</t>
         </is>
@@ -1662,7 +1668,7 @@
           <t>PC211</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>8: 4 группы × 2 MIMO-ветви, по одному объединению B3/B1/B7 на каждый головной фидер</t>
         </is>
@@ -1674,7 +1680,7 @@
           <t>Фидеры</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>7/8 — все головные и подгрупповые участки и оконечные длиннее 15 м; 1/2 — короткие оконечные. Метраж схемы ×2 MIMO, затем +10% отдельного закупочного резерва. Правило 15 м — проектное решение, джамперы отдельно.</t>
         </is>
@@ -1686,7 +1692,7 @@
           <t>Разъёмы</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>По два на каждый ненулевой изготовляемый участок фидера. Для связи с male/male джампером оконечный разъём фидера должен быть female; у делителя — male. Пол разъёмов 1/2 и 7/8 в перечне не задан, доступность модификаций не подтверждена. Интерфейсы БС и In06 также не указаны.</t>
         </is>
@@ -1698,7 +1704,7 @@
           <t>113 джамперов</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>18 входов LTE + 1 вход GSM + 2 связи после PC250 + 24 связи PC221→PC211 + 64 антенных + 4 местных связей S→Q. При подключённом только МТС 12 входных связей зарезервированы. Порты БС и пригодность длины 3 м не подтверждены.</t>
         </is>
@@ -1710,7 +1716,7 @@
           <t>Местные связи</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>4 местных соединений: геометрическая длина 0 м означает соседние устройства; соединение выполнено джампером 3 м, по два на ID для MIMO. Добавлено 0,2 дБ на путь, собственное допущение. Монтажные фидеры и отдельные разъёмы для этих связей не считаются.</t>
         </is>
@@ -1722,7 +1728,7 @@
           <t>GSM-интерфейс</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Один общий RF-выход GSM с двумя TRX принят условно: объединение передатчиков внутри БС не подтверждено. При раздельных RF-выходах требуется дополнительное решение объединения, отсутствующее в исходных данных. Отдельные входы DCS двух других операторов не выделены.</t>
         </is>
@@ -1734,7 +1740,7 @@
           <t>Неиспользуемые порты</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>У B1/B7 гибридов остаются 4 незадействованных входа, а до подключения других операторов ещё 12. Нужны согласованные 50-омные нагрузки: их нет в разрешённом перечне; это открытое несоответствие, не выдуманная позиция спецификации.</t>
         </is>
@@ -1746,7 +1752,7 @@
           <t>Потери компонентов</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Кроме 6 дБ PC221 и идеального деления паспортные потери не заданы. Использованы сценарные оценки, см. RF-лист.</t>
         </is>
@@ -1758,7 +1764,7 @@
           <t>Пожарное исполнение</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>XLSX требует огнестойкую безгалогеновую оболочку; PDF описывают PE-варианты. Нужна допустимая модификация.</t>
         </is>
@@ -1770,7 +1776,7 @@
           <t>ВК</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Проектная координата (9.2, 31.2); существующая ВК в DWG не найдена. Выделение части 104.2 под аппаратную — собственное решение, не исходное назначение комнаты.</t>
         </is>
@@ -1782,7 +1788,7 @@
           <t>Удалённое управление</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>В перечне нет подходящих управляемых модулей. Пассивная схема не подтверждает требование регулировки на удалённых модулях.</t>
         </is>
@@ -1874,7 +1880,7 @@
       <c r="E2" s="5" t="n">
         <v>28.4397</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -1900,7 +1906,7 @@
       <c r="E3" s="7" t="n">
         <v>28.1914</v>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -1926,7 +1932,7 @@
       <c r="E4" s="5" t="n">
         <v>15.6385</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -1952,7 +1958,7 @@
       <c r="E5" s="7" t="n">
         <v>61.9612</v>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -1978,7 +1984,7 @@
       <c r="E6" s="5" t="n">
         <v>5.6192</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2004,7 +2010,7 @@
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
         </is>
@@ -2030,7 +2036,7 @@
       <c r="E8" s="5" t="n">
         <v>0.4444</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2056,7 +2062,7 @@
       <c r="E9" s="7" t="n">
         <v>36.4366</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2082,7 +2088,7 @@
       <c r="E10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Соседние устройства: два заводских джампера по 3 м; не нулевой фидер</t>
         </is>
@@ -2108,7 +2114,7 @@
       <c r="E11" s="7" t="n">
         <v>16.5322</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2134,7 +2140,7 @@
       <c r="E12" s="5" t="n">
         <v>27.4515</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2160,7 +2166,7 @@
       <c r="E13" s="7" t="n">
         <v>11.5469</v>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2186,7 +2192,7 @@
       <c r="E14" s="5" t="n">
         <v>18.6482</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2212,7 +2218,7 @@
       <c r="E15" s="7" t="n">
         <v>25.2522</v>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2238,7 +2244,7 @@
       <c r="E16" s="5" t="n">
         <v>38.8312</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2264,7 +2270,7 @@
       <c r="E17" s="7" t="n">
         <v>45.6789</v>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2290,7 +2296,7 @@
       <c r="E18" s="5" t="n">
         <v>101.9669</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2316,7 +2322,7 @@
       <c r="E19" s="7" t="n">
         <v>8.978899999999999</v>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2342,7 +2348,7 @@
       <c r="E20" s="5" t="n">
         <v>3.3051</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2368,7 +2374,7 @@
       <c r="E21" s="7" t="n">
         <v>78.9036</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2394,7 +2400,7 @@
       <c r="E22" s="5" t="n">
         <v>74.8171</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2420,7 +2426,7 @@
       <c r="E23" s="7" t="n">
         <v>8.8942</v>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2446,7 +2452,7 @@
       <c r="E24" s="5" t="n">
         <v>73.27679999999999</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2472,7 +2478,7 @@
       <c r="E25" s="7" t="n">
         <v>52.7212</v>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2498,7 +2504,7 @@
       <c r="E26" s="5" t="n">
         <v>17.9207</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2524,7 +2530,7 @@
       <c r="E27" s="7" t="n">
         <v>57.066</v>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2550,7 +2556,7 @@
       <c r="E28" s="5" t="n">
         <v>1.2682</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2576,7 +2582,7 @@
       <c r="E29" s="7" t="n">
         <v>10.6708</v>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2602,7 +2608,7 @@
       <c r="E30" s="5" t="n">
         <v>13.8075</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2628,7 +2634,7 @@
       <c r="E31" s="7" t="n">
         <v>6.8864</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2654,7 +2660,7 @@
       <c r="E32" s="5" t="n">
         <v>14.127</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2680,7 +2686,7 @@
       <c r="E33" s="7" t="n">
         <v>43.8618</v>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2706,7 +2712,7 @@
       <c r="E34" s="5" t="n">
         <v>5.3998</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2732,7 +2738,7 @@
       <c r="E35" s="7" t="n">
         <v>12.3759</v>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2758,7 +2764,7 @@
       <c r="E36" s="5" t="n">
         <v>33.9558</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2784,7 +2790,7 @@
       <c r="E37" s="7" t="n">
         <v>7.77</v>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2810,7 +2816,7 @@
       <c r="E38" s="5" t="n">
         <v>1.8352</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2836,7 +2842,7 @@
       <c r="E39" s="7" t="n">
         <v>91.08629999999999</v>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2862,7 +2868,7 @@
       <c r="E40" s="5" t="n">
         <v>5.0656</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2888,7 +2894,7 @@
       <c r="E41" s="7" t="n">
         <v>118.3848</v>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2914,7 +2920,7 @@
       <c r="E42" s="5" t="n">
         <v>64.38630000000001</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2940,7 +2946,7 @@
       <c r="E43" s="7" t="n">
         <v>70.38939999999999</v>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2966,7 +2972,7 @@
       <c r="E44" s="5" t="n">
         <v>0.1325</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -2992,7 +2998,7 @@
       <c r="E45" s="7" t="n">
         <v>63.7964</v>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Проектная аппроксимация CAD-лотков; без запаса</t>
         </is>
@@ -11969,7 +11975,7 @@
       </c>
     </row>
     <row r="14" ht="51" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
         </is>
@@ -12372,7 +12378,7 @@
       </c>
     </row>
     <row r="27" ht="51" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
         </is>
@@ -12775,7 +12781,7 @@
       </c>
     </row>
     <row r="40" ht="51" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>P1_closed_gaps_geometry_uncertain_fail_RF3</t>
         </is>
@@ -18608,7 +18614,7 @@
       <c r="D2" s="5" t="n">
         <v>31.2</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Головной узел; размеры и монтажная раскладка не заданы</t>
         </is>
@@ -18631,7 +18637,7 @@
       <c r="D3" s="7" t="n">
         <v>31.2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Головной узел; размеры и монтажная раскладка не заданы</t>
         </is>
@@ -18654,7 +18660,7 @@
       <c r="D4" s="5" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Головной узел; размеры и монтажная раскладка не заданы</t>
         </is>
@@ -18723,7 +18729,7 @@
       <c r="D7" s="7" t="n">
         <v>46.02057642602261</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -18746,7 +18752,7 @@
       <c r="D8" s="5" t="n">
         <v>43.21100027232224</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -18815,7 +18821,7 @@
       <c r="D11" s="7" t="n">
         <v>30.542096</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -18838,7 +18844,7 @@
       <c r="D12" s="5" t="n">
         <v>39.986112</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -18907,7 +18913,7 @@
       <c r="D15" s="7" t="n">
         <v>26.486112</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -18930,7 +18936,7 @@
       <c r="D16" s="5" t="n">
         <v>28.115735</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -18999,7 +19005,7 @@
       <c r="D19" s="7" t="n">
         <v>4.584693</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19022,7 +19028,7 @@
       <c r="D20" s="5" t="n">
         <v>10.8684375</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19045,7 +19051,7 @@
       <c r="D21" s="7" t="n">
         <v>31.2</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Головной узел; размеры и монтажная раскладка не заданы</t>
         </is>
@@ -19068,7 +19074,7 @@
       <c r="D22" s="5" t="n">
         <v>31.2</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Головной узел; размеры и монтажная раскладка не заданы</t>
         </is>
@@ -19091,7 +19097,7 @@
       <c r="D23" s="7" t="n">
         <v>31.2</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Головной узел; размеры и монтажная раскладка не заданы</t>
         </is>
@@ -19160,7 +19166,7 @@
       <c r="D26" s="5" t="n">
         <v>46.02057642602261</v>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19183,7 +19189,7 @@
       <c r="D27" s="7" t="n">
         <v>43.21100027232224</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19252,7 +19258,7 @@
       <c r="D30" s="5" t="n">
         <v>30.542096</v>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19275,7 +19281,7 @@
       <c r="D31" s="7" t="n">
         <v>39.986112</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19344,7 +19350,7 @@
       <c r="D34" s="5" t="n">
         <v>26.486112</v>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19367,7 +19373,7 @@
       <c r="D35" s="7" t="n">
         <v>28.115735</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19436,7 +19442,7 @@
       <c r="D38" s="5" t="n">
         <v>4.584693</v>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19459,7 +19465,7 @@
       <c r="D39" s="7" t="n">
         <v>10.8684375</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
         </is>
@@ -19505,7 +19511,7 @@
       <c r="D41" s="7" t="n">
         <v>49.02438226281524</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19528,7 +19534,7 @@
       <c r="D42" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19551,7 +19557,7 @@
       <c r="D43" s="7" t="n">
         <v>63.42404058032748</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19574,7 +19580,7 @@
       <c r="D44" s="5" t="n">
         <v>59.99460955452709</v>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19597,7 +19603,7 @@
       <c r="D45" s="7" t="n">
         <v>49.02438226281524</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19620,7 +19626,7 @@
       <c r="D46" s="5" t="n">
         <v>46.02057642602261</v>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19643,7 +19649,7 @@
       <c r="D47" s="7" t="n">
         <v>43.21100027232224</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19666,7 +19672,7 @@
       <c r="D48" s="5" t="n">
         <v>40.21100027232223</v>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19689,7 +19695,7 @@
       <c r="D49" s="7" t="n">
         <v>50.48999999999999</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19712,7 +19718,7 @@
       <c r="D50" s="5" t="n">
         <v>26.095</v>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19735,7 +19741,7 @@
       <c r="D51" s="7" t="n">
         <v>60.20952398557016</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19758,7 +19764,7 @@
       <c r="D52" s="5" t="n">
         <v>33.62879322850282</v>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19781,7 +19787,7 @@
       <c r="D53" s="7" t="n">
         <v>47.28251056928649</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19804,7 +19810,7 @@
       <c r="D54" s="5" t="n">
         <v>46.83554124130971</v>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19827,7 +19833,7 @@
       <c r="D55" s="7" t="n">
         <v>40.62021820570461</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19850,7 +19856,7 @@
       <c r="D56" s="5" t="n">
         <v>35.32850186609248</v>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19873,7 +19879,7 @@
       <c r="D57" s="7" t="n">
         <v>20.56811553916096</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19896,7 +19902,7 @@
       <c r="D58" s="5" t="n">
         <v>30.86086281460469</v>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19919,7 +19925,7 @@
       <c r="D59" s="7" t="n">
         <v>23.56811553916096</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19942,7 +19948,7 @@
       <c r="D60" s="5" t="n">
         <v>21.26786214284159</v>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19965,7 +19971,7 @@
       <c r="D61" s="7" t="n">
         <v>30.792355587748</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -19988,7 +19994,7 @@
       <c r="D62" s="5" t="n">
         <v>30.71789008037059</v>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20011,7 +20017,7 @@
       <c r="D63" s="7" t="n">
         <v>24.58</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20034,7 +20040,7 @@
       <c r="D64" s="5" t="n">
         <v>27.93276712019818</v>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20057,7 +20063,7 @@
       <c r="D65" s="7" t="n">
         <v>3.667097893003584</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20080,7 +20086,7 @@
       <c r="D66" s="5" t="n">
         <v>12.4507421875</v>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20103,7 +20109,7 @@
       <c r="D67" s="7" t="n">
         <v>17.345</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20126,7 +20132,7 @@
       <c r="D68" s="5" t="n">
         <v>21.87877117801221</v>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20149,7 +20155,7 @@
       <c r="D69" s="7" t="n">
         <v>4.16375</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20172,7 +20178,7 @@
       <c r="D70" s="5" t="n">
         <v>2.132269541326413</v>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20195,7 +20201,7 @@
       <c r="D71" s="7" t="n">
         <v>10.8684375</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="11" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>
@@ -20218,7 +20224,7 @@
       <c r="D72" s="5" t="n">
         <v>5.653403907351852</v>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
         </is>

--- a/equipment/bill-of-materials.xlsx
+++ b/equipment/bill-of-materials.xlsx
@@ -8,51 +8,43 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исходный перечень" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статус" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Трассы" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RF и RSRP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие сценарии" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие помещения" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Портовый план" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Размещение" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCS сценарии" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Комплектность" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Трассы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RF и RSRP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие сценарии" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие помещения" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Портовый план" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Размещение" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCS сценарии" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Комплектность" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Спецификация'!$A$1:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Спецификация'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Спецификация'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Исходный перечень'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Исходный перечень'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Исходный перечень'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Статус'!$A$1:$B$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Статус'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Статус'!$A$1:$B$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Трассы'!$A$1:$F$45</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Трассы'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Трассы'!$A$1:$F$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RF и RSRP'!$A$1:$F$385</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'RF и RSRP'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'RF и RSRP'!$A$1:$F$385</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Покрытие сценарии'!$A$1:$I$40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Покрытие сценарии'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Покрытие сценарии'!$A$1:$I$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Покрытие помещения'!$A$1:$F$109</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Покрытие помещения'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Покрытие помещения'!$A$1:$F$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Портовый план'!$A$1:$D$138</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Портовый план'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Портовый план'!$A$1:$D$138</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Размещение'!$A$1:$E$72</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Размещение'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Размещение'!$A$1:$E$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'DCS сценарии'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'DCS сценарии'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'DCS сценарии'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Комплектность'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Комплектность'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Комплектность'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Трассы'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Трассы'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Трассы'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RF и RSRP'!$A$1:$F$385</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'RF и RSRP'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'RF и RSRP'!$A$1:$F$385</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Покрытие сценарии'!$A$1:$I$40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Покрытие сценарии'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Покрытие сценарии'!$A$1:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Покрытие помещения'!$A$1:$F$109</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Покрытие помещения'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Покрытие помещения'!$A$1:$F$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Портовый план'!$A$1:$D$138</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Портовый план'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Портовый план'!$A$1:$D$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Размещение'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Размещение'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Размещение'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DCS сценарии'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'DCS сценарии'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'DCS сценарии'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Комплектность'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Комплектность'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Комплектность'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -574,14 +566,14 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>In06_Потолочная, омни, MIMO, 800-2700 (G= 3dBi, H=360°)</t>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>In06 — потолочная MIMO-антенна</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Потолочная omni, MIMO; 800–2700 МГц; G=3 dBi; H=360°. Вертикальная диаграмма не предоставлена.</t>
+          <t>800–2700 МГц; номинальное усиление 3 dBi; азимут 360°. Два независимых RF-порта.</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
@@ -599,14 +591,14 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>PC211 Триплексер 1710-1880/1920-2170/2500-2690 МГц, одинарный, 4.3-10F, -160дБн, IP67</t>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>PC211 — триплексер</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Триплексер 1710–1880 / 1920–2170 / 2500–2690 МГц, одинарный; 4.3-10F; IP67. Insertion loss не дано.</t>
+          <t>1710–1880 / 1920–2170 / 2500–2690 МГц; 4.3-10F; IP67. Расчётные потери — 1 дБ.</t>
         </is>
       </c>
       <c r="D3" s="7" t="n">
@@ -624,14 +616,14 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>PC221_Гибридный комбайнер, 6дБ, 790-2700 МГц, 4.3-10F, -160дБн, IP65 (Комбайнер 4х4, 8 портов)</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>PC221 — гибридный комбайнер 4×4</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Гибрид 4×4, 8 портов; 790–2700 МГц; 6 дБ; 4.3-10F; IP65. Изоляция и допустимая мощность не даны.</t>
+          <t>790–2700 МГц; 8 портов; распределение 6 дБ; 4.3-10F; IP65.</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -649,14 +641,14 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>PC250_Делитель мощности, 2:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>PC250 — делитель мощности 2:1</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Делитель 2:1; 700–2700 МГц; 4.3-10F; IP65. Идеальное деление 3,01 дБ, excess loss не дано.</t>
+          <t>700–2700 МГц; 4.3-10F; IP65. Идеальное деление 3,01 дБ; дополнительные потери приняты 0,5 дБ.</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
@@ -674,14 +666,14 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>PC252_Делитель мощности, 4:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>PC252 — делитель мощности 4:1</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Делитель 4:1; 700–2700 МГц; 4.3-10F; IP65. Идеальное деление 6,02 дБ, excess loss не дано.</t>
+          <t>700–2700 МГц; 4.3-10F; IP65. Идеальное деление 6,02 дБ; дополнительные потери приняты 0,5 дБ.</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
@@ -693,20 +685,20 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Фидер коаксиальный 1/2 гибкий, оболочка - огнестойкая безгалогеновая</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Фидер коаксиальный 1/2</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>1/2, 50 Ом по PDF LCF12-50J; 10,09 / 10,99 / 12,3867 дБ/100м при 1800/2100/2600 (последние две интерполированы). Пожарная модификация не подтверждена.</t>
+          <t>50 Ом; затухание 10,09 / 10,99 / 12,3867 дБ/100 м при 1800 / 2100 / 2600 МГц по LCF12-50J, два последних значения интерполированы. Требуется огнестойкая безгалогеновая оболочка.</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
@@ -724,14 +716,14 @@
           <t>АФУ</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Фидер коаксиальный 7/8 гибкий, оболочка - огнестойкая безгалогеновая</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Фидер коаксиальный 7/8</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>7/8, 50 Ом по PDF LCF78-50JA-A0; 5,21 / 5,67 / 6,39 дБ/100м при 1800/2100/2600; допуск ±5%. Пожарная модификация не подтверждена.</t>
+          <t>50 Ом; затухание 5,21 / 5,67 / 6,39 дБ/100 м при 1800 / 2100 / 2600 МГц по LCF78-50JA-A0; допуск ±5%. Требуется огнестойкая безгалогеновая оболочка.</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -751,12 +743,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разъем 4.3-10 для 1/2 </t>
+          <t>Разъем 4.3-10 для фидера 1/2</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>4.3-10 для фидера 1/2. Loss, PIM и конкретная модификация не предоставлены.</t>
+          <t>34 male и 34 female; два разъёма на каждый из 34 изготовляемых участков.</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -776,12 +768,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Разъем 4.3-10 для 7/8</t>
+          <t>Разъем 4.3-10 для фидера 7/8</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>4.3-10 для фидера 7/8. Loss, PIM и конкретная модификация не предоставлены.</t>
+          <t>70 male и 30 female; два разъёма на каждый из 50 изготовляемых участков.</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -793,7 +785,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>АФУ</t>
@@ -801,12 +793,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Джамп-кабель 4.3-10m / 4.3-10m 3м</t>
+          <t>Джамп-кабель 4.3-10m / 4.3-10m, 3 м</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>4.3-10 male / 4.3-10 male, 3 м. Собственное затухание и тип кабеля не предоставлены.</t>
+          <t>Соединение male/male; 101 рабочая и 12 резервных связей. В рабочие связи входят четыре местных соединения распределителей.</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -820,374 +812,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E11"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00D82035"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Сценарий</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Мощность BCCH дБм</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Доп. потери дБ</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Доля от 2100, %</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Минимум дБм</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Модель ≥95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="21" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>D40_per_TRX</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>97.6596979825995</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>-103.8406708132619</v>
-      </c>
-      <c r="F2" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="21" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>D40_total_2TRX_equal</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>36.98970004336019</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>97.65558306260813</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>-106.8509707699017</v>
-      </c>
-      <c r="F3" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>D30_per_TRX</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>97.61633602937316</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>-113.8406708132619</v>
-      </c>
-      <c r="F4" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>D40_RF_extra3dB</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>97.65558306260813</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>-106.8406708132619</v>
-      </c>
-      <c r="F5" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F5"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00D82035"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Элемент / требование</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Количество / условие</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Основание и ограничение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Нагрузки входов, только МТС</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>50 Ом; модели и допустимые мощности не предоставлены, в основную спецификацию не добавлены</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Нагрузки входов, три LTE-оператора</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Четвёртые входы гибридов B1/B7; отдельного резерва GSM О2/О3 нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Разъёмы 1/2</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>34 male + 34 female</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Это требуемые исполнения в рамках общей позиции перечня; доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Разъёмы 7/8</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>70 male + 30 female</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Female на антенных концах для male/male джамперов; переходники не выдуманы</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>In06 / БС</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Интерфейс не задан</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>4.3-10F на In06 принят как условие стыковки, не характеристика из перечня</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Объединение двух GSM TRX</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Условно общий RF-порт БС</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>При раздельных выходах нужно дополнительное решение; его модели нет в исходных данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>DCS О2 / О3</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Отдельных входов нет</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Три LTE-оператора предусмотрены, полное трёхоператорское использование GSM не подтверждено</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Удалённое регулирование</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Не выполнено пассивной схемой</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Соответствующих модулей в перечне нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>PIM −160дБн</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Заявлено для пассивных компонентов в перечне</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Условия измерения, допустимая суммарная мощность и изоляция не предоставлены</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Пожарное исполнение</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>XLSX: огнестойкое, безгалогеновое; PDF: PE</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Расчёт затухания по PDF не подтверждает требуемую модификацию</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C11"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -1209,614 +833,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>п.п.</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="21" customHeight="1">
-      <c r="A2" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>In06_Потолочная, омни, MIMO, 800-2700 (G= 3dBi, H=360°)</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="21" customHeight="1">
-      <c r="A3" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>In08_Панельная настенная, MIMO (G=7dBi, H=90°, V=60°)</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>PC211 Триплексер 1710-1880/1920-2170/2500-2690 МГц, одинарный, 4.3-10F, -160дБн, IP67</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>PC221_Гибридный комбайнер, 6дБ, 790-2700 МГц, 4.3-10F, -160дБн, IP65 (Комбайнер 4х4, 8 портов)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>PC250_Делитель мощности, 2:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>PC251_Делитель мощности, 3:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>PC252_Делитель мощности, 4:1, 700-2700 МГц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>PC241_Направленный ответвитель, 7 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>PC243_Направленный ответвитель, 10 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>PC244_Направленный ответвитель, 13 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>PC245_Направленный ответвитель, 15 dB,  700-2700 Мгц, 4.3-10F, -160дБн, IP65</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Фидер коаксиальный 1/2 гибкий, оболочка - огнестойкая безгалогеновая</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Фидер коаксиальный 7/8 гибкий, оболочка - огнестойкая безгалогеновая</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Разъем 4.3-10 для 1/2 </t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Разъем 4.3-10 для 7/8</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>АФУ</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Джамп-кабель 4.3-10m / 4.3-10m 3м</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D17"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00D82035"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Позиция</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Обоснование / ограничение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Проект</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Расчётный вариант финала с явно указанными ограничениями; не комплект для закупки без проверки паспортов и условий монтажа</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>32 антенн</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Проектные точки выбраны из CAD-привязок и сравнения покрытия. Координаты, распределение и исходные IDs — в project-input.json. Помещение 89 не локализовано.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Дерево на одну MIMO-ветвь</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>PC221: 4 выхода → 4 PC211 → 4 зоны. В каждой зоне PC252: два выхода напрямую на две антенны; третий через PC250 на две; четвёртый через PC252 на четыре. Доли мощности 1/4, 1/8, 1/16; 2+2+4=8 антенн.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>6: 3 диапазона × 2 MIMO-ветви. По три входа для операторов; четвёртый B3 для GSM МТС. Все четыре выхода используются. Неизвестные мощности других операторов не подставлены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>9: один делит DCS-пул на два гибрида B3; восемь питают парные подгруппы, по одному на зону/ветвь.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>8: 4 группы × 2 MIMO-ветви, по одному объединению B3/B1/B7 на каждый головной фидер</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Фидеры</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>7/8 — все головные и подгрупповые участки и оконечные длиннее 15 м; 1/2 — короткие оконечные. Метраж схемы ×2 MIMO, затем +10% отдельного закупочного резерва. Правило 15 м — проектное решение, джамперы отдельно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="51" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Разъёмы</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>По два на каждый ненулевой изготовляемый участок фидера. Для связи с male/male джампером оконечный разъём фидера должен быть female; у делителя — male. Пол разъёмов 1/2 и 7/8 в перечне не задан, доступность модификаций не подтверждена. Интерфейсы БС и In06 также не указаны.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="51" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>113 джамперов</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>18 входов LTE + 1 вход GSM + 2 связи после PC250 + 24 связи PC221→PC211 + 64 антенных + 4 местных связей S→Q. При подключённом только МТС 12 входных связей зарезервированы. Порты БС и пригодность длины 3 м не подтверждены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="51" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Местные связи</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>4 местных соединений: геометрическая длина 0 м означает соседние устройства; соединение выполнено джампером 3 м, по два на ID для MIMO. Добавлено 0,2 дБ на путь, собственное допущение. Монтажные фидеры и отдельные разъёмы для этих связей не считаются.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>GSM-интерфейс</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Один общий RF-выход GSM с двумя TRX принят условно: объединение передатчиков внутри БС не подтверждено. При раздельных RF-выходах требуется дополнительное решение объединения, отсутствующее в исходных данных. Отдельные входы DCS двух других операторов не выделены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="51" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Неиспользуемые порты</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>У B1/B7 гибридов остаются 4 незадействованных входа, а до подключения других операторов ещё 12. Нужны согласованные 50-омные нагрузки: их нет в разрешённом перечне; это открытое несоответствие, не выдуманная позиция спецификации.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Потери компонентов</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Кроме 6 дБ PC221 и идеального деления паспортные потери не заданы. Использованы сценарные оценки, см. RF-лист.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Пожарное исполнение</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>XLSX требует огнестойкую безгалогеновую оболочку; PDF описывают PE-варианты. Нужна допустимая модификация.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ВК</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Проектная координата (9.2, 31.2); существующая ВК в DWG не найдена. Выделение части 104.2 под аппаратную — собственное решение, не исходное назначение комнаты.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Удалённое управление</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>В перечне нет подходящих управляемых модулей. Пассивная схема не подтверждает требование регулировки на удалённых модулях.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B17"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00D82035"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1856,7 +872,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Источник</t>
+          <t>Примечание</t>
         </is>
       </c>
     </row>
@@ -1882,7 +898,7 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -1908,7 +924,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -1934,7 +950,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -1960,7 +976,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1002,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2038,7 +1054,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2064,7 +1080,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2116,7 +1132,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2142,7 +1158,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2168,7 +1184,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2194,7 +1210,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2220,7 +1236,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2246,7 +1262,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2272,7 +1288,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2298,7 +1314,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2324,7 +1340,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2350,7 +1366,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2376,7 +1392,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2402,7 +1418,7 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2428,7 +1444,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2454,7 +1470,7 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2480,7 +1496,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2506,7 +1522,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2532,7 +1548,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2558,7 +1574,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2584,7 +1600,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2610,7 +1626,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2636,7 +1652,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2662,7 +1678,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2688,7 +1704,7 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2714,7 +1730,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2740,7 +1756,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2766,7 +1782,7 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2792,7 +1808,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2818,7 +1834,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2844,7 +1860,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2870,7 +1886,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2896,7 +1912,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2922,7 +1938,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2948,7 +1964,7 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -2974,7 +1990,7 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -3000,7 +2016,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Проектная аппроксимация CAD-лотков; без запаса</t>
+          <t>По проектной трассе лотков; без закупочного резерва</t>
         </is>
       </c>
     </row>
@@ -3020,7 +2036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D82035"/>
@@ -11534,7 +10550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D82035"/>
@@ -12827,7 +11843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D82035"/>
@@ -15485,7 +14501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D82035"/>
@@ -15519,7 +14535,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Функция соединения</t>
         </is>
       </c>
     </row>
@@ -15563,7 +14579,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -15585,7 +14601,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -15607,7 +14623,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15629,7 +14645,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15651,7 +14667,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15673,7 +14689,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15717,7 +14733,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -15739,11 +14755,11 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+          <t>Резерв LTE-оператора</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Нагрузка 50 Ом</t>
@@ -15759,9 +14775,9 @@
           <t>Не представлена в перечне</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Неукомплектовано</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Подключение нагрузки 50 Ом; изделие выбирается при комплектации</t>
         </is>
       </c>
     </row>
@@ -15783,7 +14799,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15805,7 +14821,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15827,7 +14843,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15849,7 +14865,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15893,7 +14909,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -15915,11 +14931,11 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+          <t>Резерв LTE-оператора</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Нагрузка 50 Ом</t>
@@ -15935,9 +14951,9 @@
           <t>Не представлена в перечне</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Неукомплектовано</t>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Подключение нагрузки 50 Ом; изделие выбирается при комплектации</t>
         </is>
       </c>
     </row>
@@ -15959,7 +14975,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -15981,7 +14997,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16003,7 +15019,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16025,7 +15041,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16047,7 +15063,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16069,7 +15085,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16091,7 +15107,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16113,7 +15129,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16135,7 +15151,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16157,7 +15173,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16179,7 +15195,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16201,7 +15217,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16223,7 +15239,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16245,7 +15261,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16267,7 +15283,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16289,7 +15305,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16311,7 +15327,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16333,7 +15349,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16355,7 +15371,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16377,7 +15393,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16399,7 +15415,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16421,7 +15437,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16443,7 +15459,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16465,7 +15481,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16487,7 +15503,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16509,7 +15525,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16531,7 +15547,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16553,7 +15569,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16575,7 +15591,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16597,7 +15613,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16619,7 +15635,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16641,7 +15657,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16663,7 +15679,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16685,7 +15701,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16707,7 +15723,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16729,7 +15745,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16751,7 +15767,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16773,7 +15789,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16795,7 +15811,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16817,7 +15833,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16839,7 +15855,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16861,7 +15877,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16883,7 +15899,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16905,7 +15921,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16927,7 +15943,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16949,7 +15965,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16971,7 +15987,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -16993,7 +16009,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17037,7 +16053,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -17059,7 +16075,7 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -17081,7 +16097,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17103,7 +16119,7 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17125,7 +16141,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17147,7 +16163,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17191,7 +16207,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -17213,11 +16229,11 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="21" customHeight="1">
+          <t>Резерв LTE-оператора</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Нагрузка 50 Ом</t>
@@ -17233,9 +16249,9 @@
           <t>Не представлена в перечне</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Неукомплектовано</t>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Подключение нагрузки 50 Ом; изделие выбирается при комплектации</t>
         </is>
       </c>
     </row>
@@ -17257,7 +16273,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17279,7 +16295,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17301,7 +16317,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17323,7 +16339,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17367,7 +16383,7 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
+          <t>Резерв LTE-оператора</t>
         </is>
       </c>
     </row>
@@ -17389,11 +16405,11 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Резерв, мощность не задана</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="21" customHeight="1">
+          <t>Резерв LTE-оператора</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Нагрузка 50 Ом</t>
@@ -17409,9 +16425,9 @@
           <t>Не представлена в перечне</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Неукомплектовано</t>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Подключение нагрузки 50 Ом; изделие выбирается при комплектации</t>
         </is>
       </c>
     </row>
@@ -17433,7 +16449,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17455,7 +16471,7 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17477,7 +16493,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17499,7 +16515,7 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17521,7 +16537,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17543,7 +16559,7 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17565,7 +16581,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17587,7 +16603,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17609,7 +16625,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17631,7 +16647,7 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17653,7 +16669,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17675,7 +16691,7 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17697,7 +16713,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17719,7 +16735,7 @@
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17741,7 +16757,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17763,7 +16779,7 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17785,7 +16801,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17807,7 +16823,7 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17829,7 +16845,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17851,7 +16867,7 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17873,7 +16889,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17895,7 +16911,7 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17917,7 +16933,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17939,7 +16955,7 @@
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17961,7 +16977,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -17983,7 +16999,7 @@
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18005,7 +17021,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18027,7 +17043,7 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18049,7 +17065,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18071,7 +17087,7 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18093,7 +17109,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18115,7 +17131,7 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18137,7 +17153,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18159,7 +17175,7 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18181,7 +17197,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18203,7 +17219,7 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18225,7 +17241,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18247,7 +17263,7 @@
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18269,7 +17285,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18291,7 +17307,7 @@
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18313,7 +17329,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18335,7 +17351,7 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18357,7 +17373,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18379,7 +17395,7 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18401,7 +17417,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18423,7 +17439,7 @@
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18445,7 +17461,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18467,11 +17483,11 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="21" customHeight="1">
+          <t>Соединение RF-тракта</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="36" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
         <is>
           <t>GSM:COMMON (2 TRX)</t>
@@ -18487,9 +17503,9 @@
           <t>Джампер 3 м</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>Общий выход БС принят условно</t>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Общий RF-выход двух GSM TRX (условие расчёта)</t>
         </is>
       </c>
     </row>
@@ -18511,7 +17527,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18533,7 +17549,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Проект</t>
+          <t>Соединение RF-тракта</t>
         </is>
       </c>
     </row>
@@ -18542,6 +17558,1853 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D82035"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="110" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>X, м</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Y, м</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Проектная зона</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>H-B3-M1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел, проектная зона 104.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>H-B1-M1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел, проектная зона 104.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>H-B7-M1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел, проектная зона 104.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>TP-Z1-M1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>S-Z1-M1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>43.21100027232224</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M1</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>46.02057642602261</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>43.21100027232224</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>TP-Z2-M1</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>S-Z2-M1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>22.63781769212248</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>31.41208068932767</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>39.986112</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>TP-Z3-M1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>S-Z3-M1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11.37315902428026</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>26.486112</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>11.37315902428026</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>26.486112</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4.736673</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>28.115735</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>TP-Z4-M1</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>S-Z4-M1</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>16.64188377635066</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>2.98386788680957</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>4.584693</v>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>10.8684375</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>H-B3-M2</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел, проектная зона 104.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>H-B1-M2</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел, проектная зона 104.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>H-B7-M2</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>PC221</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Головной узел, проектная зона 104.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TP-Z1-M2</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>S-Z1-M2</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>43.21100027232224</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z1-1-M2</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>46.02057642602261</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z1-2-M2</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>11.40886</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>43.21100027232224</v>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TP-Z2-M2</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>S-Z2-M2</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>22.63781769212248</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z2-1-M2</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>30.542096</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z2-2-M2</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>31.41208068932767</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>39.986112</v>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TP-Z3-M2</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>S-Z3-M2</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>11.37315902428026</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>26.486112</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z3-1-M2</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>11.37315902428026</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>26.486112</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z3-2-M2</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>4.736673</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>28.115735</v>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TP-Z4-M2</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>PC211</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Головной узел</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>S-Z4-M2</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>16.64188377635066</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Зональное распределение по трассе</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Q-Z4-1-M2</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>2.98386788680957</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>4.584693</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Q-Z4-2-M2</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>PC252</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>1.315304</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>10.8684375</v>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Подгруппа на трассе; отдельные устройства M1/M2 в одной проектной зоне</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>S-DCS</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>PC250</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Головной узел; подключение общего RF-выхода GSM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>14.91956208510882</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>49.02438226281524</v>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>17.81482442176836</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>63.42404058032748</v>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>1.091118794241845</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>59.99460955452709</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>21.437444429408</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>49.02438226281524</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>6.919409400363969</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>46.02057642602261</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>13.06139527504399</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>43.21100027232224</v>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>24.15567090665015</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>40.21100027232223</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>50.48999999999999</v>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>26.095</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>32.8720806893277</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>60.20952398557016</v>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>35.32895091386823</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>33.62879322850282</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>33.07601869054855</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>47.28251056928649</v>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>35.52368472074298</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>46.83554124130971</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>31.41208068932767</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>40.62021820570461</v>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>32.08988086464296</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>35.32850186609248</v>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>14.37315902428026</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>20.56811553916096</v>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>6.815109400363969</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>30.86086281460469</v>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>17.75628876497632</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>23.56811553916096</v>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>4.71085836381269</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>21.26786214284159</v>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>5.09031425843235</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>30.792355587748</v>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0.3757184834514796</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>30.71789008037059</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>1.034618740440041</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>27.93276712019818</v>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>2.98386788680957</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>3.667097893003584</v>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>26.9351953125</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>12.4507421875</v>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>3.145</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>17.345</v>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>33.49358964038934</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>21.87877117801221</v>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="21" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>26.80375</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>4.16375</v>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>A30</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>27.77381178875924</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>2.132269541326413</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>1.3815625</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>10.8684375</v>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>A32</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>In06</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>34.76515714743073</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>5.653403907351852</v>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Проектная точка антенны; доступность места установки проверяется при монтаже</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E72"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D82035"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Мощность BCCH дБм</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Доп. потери дБ</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Доля от 2100, %</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Минимум дБм</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Модель ≥95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>D40_per_TRX</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>-103.8406708132619</v>
+      </c>
+      <c r="F2" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>D40_total_2TRX_equal</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>36.98970004336019</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>-106.8509707699017</v>
+      </c>
+      <c r="F3" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>D30_per_TRX</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>97.61633602937316</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-113.8406708132619</v>
+      </c>
+      <c r="F4" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>D40_RF_extra3dB</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>-106.8406708132619</v>
+      </c>
+      <c r="F5" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
@@ -18560,1678 +19423,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="110" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Элемент / требование</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Количество / условие</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>X, м</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Y, м</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Основание / ограничение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="21" customHeight="1">
+          <t>Техническое условие</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>H-B3-M1</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="21" customHeight="1">
+          <t>Нагрузки входов, только МТС</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Оконечные нагрузки 50 Ом. Модель и допустимая мощность определяются при комплектации; изделия отсутствуют в предоставленном перечне.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>H-B1-M1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1">
+          <t>Нагрузки входов, три LTE-оператора</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Оконечные нагрузки 50 Ом на четвёртых входах гибридов B1/B7; требования к выбору те же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>H-B7-M1</t>
+          <t>Разъёмы 1/2</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1">
+          <t>34 male + 34 female</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Male на входах распределителей, female для соединения с джамперами. Поставочное исполнение выбирается по соответствующему типоразмеру кабеля.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>TP-Z1-M1</t>
+          <t>Разъёмы 7/8</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1">
+          <t>70 male + 30 female</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Female на антенных концах, male на остальных соединениях фидеров с пассивными компонентами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>S-Z1-M1</t>
+          <t>In06 / БС</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>11.40886</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>43.21100027232224</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21" customHeight="1">
+          <t>Стыковка 4.3-10</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>4.3-10F на In06 принят как условие проекта; интерфейсы антенн и БС проверяются по поставочным исполнениям.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Q-Z1-1-M1</t>
+          <t>Объединение двух GSM TRX</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>11.40886</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>46.02057642602261</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+          <t>Общий RF-порт БС — условие расчёта</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>При раздельных выходах TRX требуется узел объединения. Его модель в исходных материалах не задана.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Q-Z1-2-M1</t>
+          <t>DCS О2 / О3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>11.40886</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>43.21100027232224</v>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
+          <t>Отдельные входы не предусмотрены</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Предусмотрены три LTE-оператора и один GSM-пул МТС.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>TP-Z2-M1</t>
+          <t>Управляемые удалённые модули</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21" customHeight="1">
+          <t>Не входят в состав пассивной сети</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Архитектура содержит пассивные элементы распределения сигнала.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>S-Z2-M1</t>
+          <t>PIM −160 дБн</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>22.63781769212248</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>30.542096</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+          <t>Параметр перечня пассивных компонентов</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Условия измерения PIM, допустимая суммарная мощность и изоляция проверяются по паспортам выбранных исполнений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Q-Z2-1-M1</t>
+          <t>Пожарное исполнение</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>30.542096</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z2-2-M1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>31.41208068932767</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>39.986112</v>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>TP-Z3-M1</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>S-Z3-M1</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>11.37315902428026</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>26.486112</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Q-Z3-1-M1</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>11.37315902428026</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>26.486112</v>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z3-2-M1</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>4.736673</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>28.115735</v>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>TP-Z4-M1</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>S-Z4-M1</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1.315304</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>16.64188377635066</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Q-Z4-1-M1</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>2.98386788680957</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>4.584693</v>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z4-2-M1</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>1.315304</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>10.8684375</v>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>H-B3-M2</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>H-B1-M2</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>H-B7-M2</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>PC221</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Головной узел; размеры и монтажная раскладка не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>TP-Z1-M2</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>S-Z1-M2</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>11.40886</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>43.21100027232224</v>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z1-1-M2</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>11.40886</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>46.02057642602261</v>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Q-Z1-2-M2</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>11.40886</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>43.21100027232224</v>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>TP-Z2-M2</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>S-Z2-M2</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>22.63781769212248</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>30.542096</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z2-1-M2</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>30.542096</v>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Q-Z2-2-M2</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>31.41208068932767</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>39.986112</v>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>TP-Z3-M2</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>S-Z3-M2</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>11.37315902428026</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>26.486112</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z3-1-M2</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>11.37315902428026</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>26.486112</v>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="21" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Q-Z3-2-M2</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>4.736673</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>28.115735</v>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>TP-Z4-M2</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>PC211</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Головной узел</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="21" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>S-Z4-M2</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>1.315304</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>16.64188377635066</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Зональное распределение по трассе</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="21" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Q-Z4-1-M2</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>2.98386788680957</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>4.584693</v>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="21" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Q-Z4-2-M2</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>PC252</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>1.315304</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>10.8684375</v>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>Подгруппа на трассе; M1/M2 показаны одной геометрической точкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="21" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>S-DCS</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>PC250</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Головной узел; общий GSM-выход условен</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="21" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>14.91956208510882</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>49.02438226281524</v>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="21" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="21" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>17.81482442176836</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>63.42404058032748</v>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="21" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>1.091118794241845</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>59.99460955452709</v>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="21" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>21.437444429408</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>49.02438226281524</v>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="21" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>6.919409400363969</v>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>46.02057642602261</v>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>13.06139527504399</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>43.21100027232224</v>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>24.15567090665015</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>40.21100027232223</v>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>50.48999999999999</v>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="21" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>26.095</v>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="21" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>A11</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>32.8720806893277</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>60.20952398557016</v>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>A12</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>35.32895091386823</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>33.62879322850282</v>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="21" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>A13</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>33.07601869054855</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>47.28251056928649</v>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>A14</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>35.52368472074298</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>46.83554124130971</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="21" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>A15</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>31.41208068932767</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>40.62021820570461</v>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>A16</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>32.08988086464296</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>35.32850186609248</v>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>A17</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>14.37315902428026</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>20.56811553916096</v>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="21" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>6.815109400363969</v>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>30.86086281460469</v>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="21" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>17.75628876497632</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>23.56811553916096</v>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="21" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>4.71085836381269</v>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>21.26786214284159</v>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="n">
-        <v>5.09031425843235</v>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>30.792355587748</v>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>A22</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>0.3757184834514796</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>30.71789008037059</v>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="21" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>A23</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="21" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>A24</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>1.034618740440041</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>27.93276712019818</v>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>A25</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="n">
-        <v>2.98386788680957</v>
-      </c>
-      <c r="D65" s="7" t="n">
-        <v>3.667097893003584</v>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="21" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>A26</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>26.9351953125</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>12.4507421875</v>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>A27</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>3.145</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>17.345</v>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>A28</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>33.49358964038934</v>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>21.87877117801221</v>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="21" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>A29</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>26.80375</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>4.16375</v>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="21" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>A30</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>27.77381178875924</v>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>2.132269541326413</v>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="21" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>A31</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="n">
-        <v>1.3815625</v>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>10.8684375</v>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="21" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>A32</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>In06</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>34.76515714743073</v>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>5.653403907351852</v>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>Исследовательская позиция n=3; монтажная доступность не подтверждена</t>
+          <t>Огнестойкая безгалогеновая оболочка</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Паспорта затухания описывают PE-исполнения. При поставке требуется пожарная модификация с подтверждёнными RF-характеристиками.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E72"/>
+  <autoFilter ref="A1:C11"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>

--- a/equipment/bill-of-materials.xlsx
+++ b/equipment/bill-of-materials.xlsx
@@ -16,6 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Размещение" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCS сценарии" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Комплектность" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTE качество" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет помех" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCS C-I" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Спецификация'!$A$1:$E$11</definedName>
@@ -45,6 +48,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Комплектность'!$A$1:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Комплектность'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Комплектность'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'LTE качество'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'LTE качество'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'LTE качество'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Бюджет помех'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Бюджет помех'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Бюджет помех'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'DCS C-I'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'DCS C-I'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'DCS C-I'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -826,6 +838,2109 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D82035"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>МГц</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>NF, дБ</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>I, дБм/15 кГц</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>β</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>SINR ≥17, %</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>SINR ≥7, %</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>SINR ≥1, %</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>RSRQ &gt;−12, %</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>RSRP &gt;−90, %</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>RSRP, SINR и RSRQ выполнены</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>L0 — Только тепловой шум</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Только шум</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>97.29312181070115</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>97.62797507227215</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L2" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>L1 — Помехи −125 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>-125</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>97.2453619648536</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>97.61899943885449</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L3" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>L2 — Помехи −115 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>96.83829011862764</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>97.2838110093962</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>97.6016940086499</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>97.61618785557125</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L4" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>L3 — Помехи −105 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>-105</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>96.48098303202424</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>96.86324523929012</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>97.20244747735704</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>97.22727287005726</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L5" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>L4 — Равная EPRE данных и CRS</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>97.18115620910267</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>97.39553026569796</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>97.62797507227215</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L6" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>L5 — Полная загрузка</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>96.83829011862764</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>97.2838110093962</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>97.6016940086499</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>97.56254170347117</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L7" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>L6 — n=3</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>96.5848873242371</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>97.19590003980055</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>97.29561983056342</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>97.31632145002476</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>96.48008553440121</v>
+      </c>
+      <c r="L8" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>L7 — Пилот P2</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>96.53813080945964</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>97.12639709887755</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>97.25654171620842</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>97.26677905578957</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>94.48982614645337</v>
+      </c>
+      <c r="L9" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>L8 — NF=9 дБ</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>96.82265835162781</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>97.28040461867488</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>97.6016940086499</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>97.60999174155553</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L10" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>L9 — Помехи −95 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>-95</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>27.43255113970781</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>96.48128384479722</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>96.5929501019443</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>96.64973581483454</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L11" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>L10 — Помехи −85 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>27.47221911018481</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>89.45349332677146</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>92.31498943061669</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>96.58558303759173</v>
+      </c>
+      <c r="L12" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>L0 — Только тепловой шум</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Только шум</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>97.28971541997983</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>97.62797507227215</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L13" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>L1 — Помехи −125 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>97.23840996426092</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>97.61693538753259</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L14" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>L2 — Помехи −115 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>96.80305015480218</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>97.28040461867488</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>97.59251340467976</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>97.6016940086499</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L15" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>L3 — Помехи −105 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-105</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>96.47907310965617</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>96.83829011862764</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>97.19917375857879</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>97.21249207397757</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L16" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>L4 — Равная EPRE данных и CRS</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>97.16314420174537</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>97.33404486851155</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>97.62705843101422</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L17" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>L5 — Полная загрузка</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>96.80305015480218</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>97.28040461867488</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>97.59251340467976</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>97.53667689399175</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L18" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>L6 — n=3</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>96.5847678932012</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>97.18935260224406</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>97.29312181070115</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>97.29811785042577</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>96.4501530203333</v>
+      </c>
+      <c r="L19" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>L7 — Пилот P2</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>96.52916226120917</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>97.09616854610125</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>97.25313532548708</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>97.26244612679206</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>93.51631857653675</v>
+      </c>
+      <c r="L20" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>L8 — NF=9 дБ</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>96.79146476570341</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>97.27699822795354</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>97.58793019839021</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>97.6016940086499</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L21" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>L9 — Помехи −95 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-95</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>24.91187883111951</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>96.47907310965617</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>96.59271123987249</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>96.59317869585587</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L22" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>L10 — Помехи −85 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>-85</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>24.95131005091287</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>87.33758005291857</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>90.84764382526971</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L23" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>L0 — Только тепловой шум</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Только шум</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>97.2838110093962</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>97.62797507227215</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L24" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>L1 — Помехи −125 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>-125</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>97.220078959144</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>97.61162287792472</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L25" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>L2 — Помехи −115 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>96.75124311418091</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>97.27359183723222</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>97.55153605617859</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>97.59251340467976</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L26" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>L3 — Помехи −105 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>-105</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>96.46707455081234</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>96.78838756137019</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>97.19917375857879</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>97.19917375857879</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L27" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>L4 — Равная EPRE данных и CRS</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>97.11898840878322</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>97.31174341331105</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>97.62244133534746</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L28" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>L5 — Полная загрузка</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>96.75124311418091</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>97.27359183723222</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>97.55153605617859</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>97.48364264978413</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L29" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>L6 — n=3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>96.58440960009351</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>97.18619411836681</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>97.29312181070115</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>97.29561983056342</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>96.36512920036991</v>
+      </c>
+      <c r="L30" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>L7 — Пилот P2</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>96.50267710652001</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>96.9865583087316</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>97.24632254404445</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>97.25654171620842</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>91.67927045131245</v>
+      </c>
+      <c r="L31" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>L8 — NF=9 дБ</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>96.74281205510262</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>97.27018544651091</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>97.54417673636507</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>97.5835645113394</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L32" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>L9 — Помехи −95 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>-95</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>21.80760357332997</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>96.47007858457664</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>96.58467117143678</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>96.5928306709084</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L33" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>L10 — Помехи −85 дБм/RE</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>21.83165092070275</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>83.91668877636957</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>88.29912773569202</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>96.58431287832906</v>
+      </c>
+      <c r="L34" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L34"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D82035"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Поле RSRP</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>МГц</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>β</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>NF, дБ</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>J предельное, дБм/15 кГц</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>I предельное, дБм/15 кГц</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>-96.22727539636651</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-96.23273141547145</v>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>P1_n3</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>-100.6160605447035</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>-100.6310653944639</v>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-104.0087879002029</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-104.0416273064333</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>-96.50712434874109</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>-96.51294375856997</v>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>P1_n3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-100.8815203534115</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-100.8974727147975</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>-104.2886368525775</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>-104.3236708568231</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-96.88209649054859</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-96.88844106370568</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>P1_n3</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>-101.2624918920179</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-101.2799097747636</v>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-104.663608994385</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-104.7018162136048</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Граница для совокупности SINR/RSRQ; рабочий уровень минимум на 0,1 дБ ниже. Параметры сценарные.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H10"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D82035"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>BCCH, дБм</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>I, дБм/200 кГц</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>C/I &gt;20, %</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>RxLev &gt;−85, %</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Оба KPI в сценарии</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>97.3049306318684</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="E2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>97.09959039368134</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="E3" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>-70</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>96.52605632396099</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="E4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>-60</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>43.66546327828119</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>97.6596979825995</v>
+      </c>
+      <c r="E5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>36.98970004336019</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>97.26677905578957</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="E6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>36.98970004336019</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>96.75100425210908</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="E7" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>36.98970004336019</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-70</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>96.22953395973002</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="E8" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>36.98970004336019</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>-60</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>15.149786947648</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>97.65558306260813</v>
+      </c>
+      <c r="E9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>97.09959039368134</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>97.61633602937316</v>
+      </c>
+      <c r="E10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>96.52605632396099</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>97.61633602937316</v>
+      </c>
+      <c r="E11" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>-70</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>43.66546327828119</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>97.61633602937316</v>
+      </c>
+      <c r="E12" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>-60</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>97.61633602937316</v>
+      </c>
+      <c r="E13" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Суммарная соканальная помеха на входе UE; ARFCN и внешние БС не заданы.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"DejaVu Sans"&amp;8 &amp;K707070МТС Engineer Hack 2026 / Радио&amp;C&amp;"DejaVu Sans"&amp;8 &amp;K70707014.10.2026&amp;R&amp;"DejaVu Sans"&amp;8 &amp;K707070&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
